--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="285">
   <si>
     <t>Notes</t>
   </si>
@@ -840,6 +840,72 @@
   </si>
   <si>
     <t>Fri Nov 21 22:02:48 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 22:23:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:17:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:20:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:23:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:26:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:03:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:08:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:12:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:16:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:17:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:18:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:19:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:20:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:21:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:24:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:28:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:29:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:32:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 20:31:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 21:00:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 21:05:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 23 20:16:12 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1297,7 +1363,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>181</v>
@@ -1335,7 +1401,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>181</v>
@@ -1373,7 +1439,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>181</v>
@@ -1411,7 +1477,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>184</v>
@@ -1452,7 +1518,7 @@
         <v>136</v>
       </c>
       <c r="B6" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>184</v>
@@ -1493,7 +1559,7 @@
         <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>184</v>
@@ -2269,7 +2335,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
@@ -2367,7 +2433,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
@@ -2465,10 +2531,10 @@
     </row>
     <row ht="30" r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>283</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2564,7 +2630,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2658,10 +2724,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2752,10 +2818,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2849,7 +2915,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2943,7 +3009,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
@@ -1,37 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cloned-Project-Katalon\VPS-Katalon\KatalonData\IWPBootstrapData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{70C3A41D-BDE7-4339-B532-54EAFDB6CDA0}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{86C148DC-7596-490E-BE52-2CA086CF6534}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="15" firstSheet="8" windowHeight="16920" windowWidth="30960" xWindow="-120" xr2:uid="{19E085DA-5ADF-4B16-9D78-B410FD3FCE3D}" yWindow="-120"/>
+    <workbookView activeTab="1" windowHeight="12456" windowWidth="23256" xWindow="-108" xr2:uid="{19E085DA-5ADF-4B16-9D78-B410FD3FCE3D}" yWindow="-108"/>
   </bookViews>
   <sheets>
     <sheet name="PayNowCC" r:id="rId1" sheetId="1"/>
-    <sheet name="PayNowCCSCF" r:id="rId2" sheetId="5"/>
-    <sheet name="PayNowCCDCF" r:id="rId3" sheetId="6"/>
-    <sheet name="DCFVerbiage" r:id="rId4" sheetId="8"/>
-    <sheet name="OverUnderPay" r:id="rId5" sheetId="9"/>
-    <sheet name="MissingCC" r:id="rId6" sheetId="4"/>
-    <sheet name="Sheet2" r:id="rId7" sheetId="3"/>
-    <sheet name="NoModifyAmount" r:id="rId8" sheetId="10"/>
-    <sheet name="NoOverPay" r:id="rId9" sheetId="11"/>
-    <sheet name="SCFVerbiage" r:id="rId10" sheetId="7"/>
-    <sheet name="Sheet1" r:id="rId11" sheetId="2"/>
-    <sheet name="NoModifyAmountCC" r:id="rId12" sheetId="12"/>
-    <sheet name="NoModifyBillingAddressCC" r:id="rId13" sheetId="13"/>
-    <sheet name="CCDeferredCC" r:id="rId14" sheetId="14"/>
-    <sheet name="CMCAutopayCC" r:id="rId15" sheetId="15"/>
-    <sheet name="PayNowCreditCardDCF" r:id="rId16" sheetId="16"/>
-    <sheet name="PayNowCreditCardSCF" r:id="rId17" sheetId="17"/>
-    <sheet name="DCFCCVerbiage" r:id="rId18" sheetId="18"/>
-    <sheet name="SCFCCVerbiage" r:id="rId19" sheetId="19"/>
+    <sheet name="PayNowCCNoCF" r:id="rId2" sheetId="22"/>
+    <sheet name="PayNowCCSCF" r:id="rId3" sheetId="5"/>
+    <sheet name="PayNowCCDCF" r:id="rId4" sheetId="6"/>
+    <sheet name="DCFVerbiage" r:id="rId5" sheetId="8"/>
+    <sheet name="OverUnderPay" r:id="rId6" sheetId="9"/>
+    <sheet name="MissingCC" r:id="rId7" sheetId="4"/>
+    <sheet name="Sheet2" r:id="rId8" sheetId="3"/>
+    <sheet name="NoModifyAmount" r:id="rId9" sheetId="10"/>
+    <sheet name="NoOverPay" r:id="rId10" sheetId="11"/>
+    <sheet name="SCFVerbiage" r:id="rId11" sheetId="7"/>
+    <sheet name="Sheet1" r:id="rId12" sheetId="2"/>
+    <sheet name="NoModifyAmountCC" r:id="rId13" sheetId="12"/>
+    <sheet name="NoModifyBillingAddressCC" r:id="rId14" sheetId="13"/>
+    <sheet name="CCDeferredCC" r:id="rId15" sheetId="14"/>
+    <sheet name="CMCAutopayCC" r:id="rId16" sheetId="15"/>
+    <sheet name="PayNowCreditCardDCF" r:id="rId17" sheetId="16"/>
+    <sheet name="ModifyPaymentsCC1" r:id="rId18" sheetId="20"/>
+    <sheet name="ModifyPaymentsCC2" r:id="rId19" sheetId="21"/>
+    <sheet name="PayNowCreditCardSCF" r:id="rId20" sheetId="17"/>
+    <sheet name="DCFCCVerbiage" r:id="rId21" sheetId="18"/>
+    <sheet name="SCFCCVerbiage" r:id="rId22" sheetId="19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="355">
   <si>
     <t>Notes</t>
   </si>
@@ -614,39 +617,15 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sat Oct 05 17:04:15 EDT 2024</t>
-  </si>
-  <si>
-    <t>Sat Oct 05 17:05:14 EDT 2024</t>
-  </si>
-  <si>
-    <t>Sat Oct 05 17:06:12 EDT 2024</t>
-  </si>
-  <si>
-    <t>Sat Oct 05 17:07:08 EDT 2024</t>
-  </si>
-  <si>
-    <t>Sat Oct 05 17:08:11 EDT 2024</t>
-  </si>
-  <si>
-    <t>Sat Oct 05 17:09:14 EDT 2024</t>
-  </si>
-  <si>
     <t>887</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Mon Jan 06 14:31:44 IST 2025</t>
-  </si>
-  <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Tue Dec 17 17:02:38 IST 2024</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
@@ -656,256 +635,490 @@
     <t>882</t>
   </si>
   <si>
-    <t>Tue Jan 07 15:19:24 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 07 15:21:09 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 07 15:23:05 IST 2025</t>
-  </si>
-  <si>
     <t>12/31/2025</t>
   </si>
   <si>
-    <t>Tue Jan 07 15:29:56 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 07 15:48:01 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Jan 31 21:43:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jun 03 23:38:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jun 03 23:43:53 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jun 03 23:47:13 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jun 03 23:50:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jun 03 23:53:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jun 03 23:54:23 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jun 03 23:55:04 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jun 03 23:55:49 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jun 03 23:56:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jun 03 23:57:26 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 04 00:00:27 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 04 00:03:24 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 04 00:05:06 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:29:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:35:23 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:39:06 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:42:31 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:45:49 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:46:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:47:23 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:48:14 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:49:03 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:49:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:52:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:56:07 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 25 00:58:07 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 00:16:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 00:17:44 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 00:19:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:01:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:11:36 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:17:29 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:22:03 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:26:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:28:47 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:30:59 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:33:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:01:06 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:02:03 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:02:57 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:03:44 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:04:36 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:05:30 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:11:56 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:14:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:16:25 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:18:25 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:44:58 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:47:59 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:48:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 19:24:34 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 19:58:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 20:07:25 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 21:46:39 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 22:02:48 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 22:23:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:17:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:20:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:23:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:26:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:03:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:08:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:12:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:16:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:17:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:18:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:19:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:20:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:21:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:24:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:28:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:29:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:32:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 20:31:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 21:00:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 21:05:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 23 20:16:12 IST 2026</t>
+    <t>Wed Feb 04 14:59:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 15:14:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 15:24:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:29:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:37:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:40:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 20:30:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 20:44:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 21:05:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 21:07:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 21:08:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 21:09:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 21:10:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 21:11:17 IST 2026</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 23:05:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 20:06:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:41:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:42:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:43:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:44:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:15:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:20:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:25:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:29:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:30:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:31:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:32:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:33:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:35:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:39:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:43:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:47:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 20:20:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 20:25:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 22:03:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 01:08:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 01:45:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 01:56:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:04:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:08:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:12:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:16:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:17:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:18:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:19:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:20:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:21:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:24:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:26:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:30:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:32:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:47:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 03:33:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 03:43:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 03:53:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:03:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:08:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:13:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:17:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:18:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:20:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:20:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:21:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:22:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:27:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:31:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:34:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:45:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:51:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:11:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:16:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:21:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:25:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:26:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:27:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:28:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:28:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:30:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:34:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:38:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 06:05:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 06:10:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 06:11:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 01:51:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 01:58:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:05:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:27:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:31:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:35:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:36:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:37:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:37:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:38:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:39:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:42:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:46:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:18:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:19:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:20:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:35:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 21:48:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 06:32:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 06:36:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 07:59:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:10:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:20:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:31:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:35:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:40:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:43:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:44:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:45:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:46:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:47:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:48:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:51:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:55:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:56:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:58:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 09:03:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 09:35:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:17:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:21:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 00:38:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 00:41:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 14:02:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 21:29:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 21:38:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 21:46:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 22:10:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 22:43:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 19:48:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 20:41:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 20:46:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 20:48:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 20:54:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 21:05:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 21:22:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 23:43:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 23:47:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 23:55:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Mar 13 00:02:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Mar 13 20:29:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Mar 13 20:34:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Mar 13 20:37:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Mar 13 20:39:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Mar 13 21:16:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Mar 13 22:00:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 16 21:13:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 16 21:16:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 16 21:36:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 17 21:47:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 17 21:54:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 17 22:07:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 17 22:14:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 17 22:26:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 18 23:35:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 00:07:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 21:07:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:19:23 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1295,26 +1508,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4684B99E-74C7-4C50-809D-02154653C064}">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="43.85546875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="12.42578125" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="43.88671875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="12.44140625" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
     <col min="11" max="11" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="14.42578125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="15.85546875" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="14.44140625" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="15.88671875" collapsed="true"/>
     <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="15" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="15" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -1358,12 +1571,12 @@
         <v>179</v>
       </c>
     </row>
-    <row ht="30" r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>181</v>
@@ -1396,12 +1609,12 @@
         <v>177</v>
       </c>
     </row>
-    <row ht="30" r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>181</v>
@@ -1434,12 +1647,12 @@
         <v>177</v>
       </c>
     </row>
-    <row ht="30" r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>181</v>
@@ -1472,12 +1685,12 @@
         <v>177</v>
       </c>
     </row>
-    <row ht="30" r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>307</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>184</v>
@@ -1513,12 +1726,12 @@
         <v>174</v>
       </c>
     </row>
-    <row ht="30" r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>136</v>
       </c>
       <c r="B6" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>184</v>
@@ -1554,12 +1767,12 @@
         <v>174</v>
       </c>
     </row>
-    <row ht="30" r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>184</v>
@@ -1606,36 +1819,31 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0998B4B-1379-4C62-AAAC-69FB8C23F4B6}">
-  <dimension ref="A1:AC5"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{133992E5-F2D4-42EB-B2FB-D66167060930}">
+  <dimension ref="A1:AC2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.28515625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="15.140625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.28515625" collapsed="true"/>
-    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
-    <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="29" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.88671875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="19.33203125" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="10.44140625" collapsed="true"/>
+    <col min="9" max="17" bestFit="true" customWidth="true" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.5546875" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.33203125" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="6.0" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row customFormat="1" r="1" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -1721,26 +1929,31 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row customFormat="1" r="2" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
-      <c r="B2"/>
+      <c r="B2" t="s">
+        <v>163</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="T2" s="1" t="s">
         <v>127</v>
       </c>
@@ -1754,18 +1967,6 @@
         <v>125</v>
       </c>
       <c r="AB2" s="2"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3"/>
-      <c r="B3"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4"/>
-      <c r="B4"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5"/>
-      <c r="B5"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1773,51 +1974,218 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0998B4B-1379-4C62-AAAC-69FB8C23F4B6}">
+  <dimension ref="A1:AC5"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB2" s="2"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3"/>
+      <c r="B3"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4"/>
+      <c r="B4"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5"/>
+      <c r="B5"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CECF72-ED76-4A08-B368-44E780FE04C9}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="38.5703125" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="38.5546875" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="4.0" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="8.28515625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="8.33203125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="6.85546875" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="13.85546875" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="13.88671875" collapsed="true"/>
     <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
     <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.42578125" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="5.5703125" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.44140625" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="5.5546875" collapsed="true"/>
     <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="6.140625" collapsed="true"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="14.7109375" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="23.85546875" collapsed="true"/>
-    <col min="18" max="23" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="24" max="24" customWidth="true" style="1" width="9.85546875" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="6.85546875" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="29" max="29" style="1" width="15.7109375" collapsed="true"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="32" max="33" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="34" max="39" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="41" max="41" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="17.28515625" collapsed="true"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="45" max="46" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="6.109375" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="14.6640625" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="23.88671875" collapsed="true"/>
+    <col min="18" max="23" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="1" width="9.88671875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.6640625" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="29" max="29" style="1" width="15.6640625" collapsed="true"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="34" max="39" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="41" max="41" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="17.33203125" collapsed="true"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="45" max="46" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="51" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="51" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1969,7 +2337,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>105</v>
       </c>
@@ -2053,7 +2421,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>106</v>
       </c>
@@ -2148,7 +2516,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>107</v>
       </c>
@@ -2281,12 +2649,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E9DE92-B397-44B0-AEC9-F8D25811CB54}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="30" r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2330,12 +2698,12 @@
         <v>179</v>
       </c>
     </row>
-    <row ht="105" r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="100.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
@@ -2347,13 +2715,13 @@
         <v>186</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>182</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>176</v>
@@ -2365,105 +2733,7 @@
         <v>123</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5A0641-6BD7-468B-84F0-EE792C70A080}">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row ht="30" r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row ht="105" r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>177</v>
@@ -2478,14 +2748,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D73A527-72BD-4591-A2D4-2CEF61283D2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5A0641-6BD7-468B-84F0-EE792C70A080}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5703125" collapsed="true"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="30" r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2529,46 +2796,48 @@
         <v>179</v>
       </c>
     </row>
-    <row ht="30" r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="100.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C2" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="D2" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>123</v>
+      <c r="H2" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>152</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>174</v>
+      <c r="N2" s="5" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2577,11 +2846,14 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF51F7AD-B3C1-42AF-94A4-9027DD404D74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D73A527-72BD-4591-A2D4-2CEF61283D2F}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
+  </cols>
   <sheetData>
-    <row ht="30" r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2625,19 +2897,19 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>354</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>183</v>
@@ -2657,7 +2929,9 @@
       <c r="K2" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="L2" s="1"/>
+      <c r="L2" s="1" t="s">
+        <v>193</v>
+      </c>
       <c r="M2" s="1" t="s">
         <v>176</v>
       </c>
@@ -2671,14 +2945,11 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAE4061-05C7-45C5-8300-61EB089304F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF51F7AD-B3C1-42AF-94A4-9027DD404D74}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" customWidth="true" width="19.85546875" collapsed="true"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="30" r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2722,22 +2993,22 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>345</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>182</v>
@@ -2768,11 +3039,14 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CCF0244-D738-49E7-A19C-75065FE186E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAE4061-05C7-45C5-8300-61EB089304F4}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" customWidth="true" width="19.88671875" collapsed="true"/>
+  </cols>
   <sheetData>
-    <row ht="30" r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2816,12 +3090,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>326</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2831,7 +3105,7 @@
         <v>186</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>182</v>
@@ -2862,11 +3136,11 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24FF721F-C1CF-4DC8-8195-832F8368F224}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53E0D33-A959-464C-9A30-B01B5F6EAEC6}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="30" r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2910,29 +3184,21 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C2" s="2"/>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C2" s="4"/>
       <c r="D2" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
         <v>123</v>
       </c>
@@ -2940,7 +3206,7 @@
         <v>152</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2956,11 +3222,11 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4992758E-A1F9-4281-AE93-21063312FF32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2B6DA3-9B51-4304-9318-F6DFDE44D446}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="30" r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3004,37 +3270,29 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C2" s="2"/>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C2" s="4"/>
       <c r="D2" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -3050,36 +3308,406 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8552FB6B-D1DF-4DF4-9CDC-DC482F51F66E}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row ht="115.2" r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C2" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CCF0244-D738-49E7-A19C-75065FE186E2}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24FF721F-C1CF-4DC8-8195-832F8368F224}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4992758E-A1F9-4281-AE93-21063312FF32}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCE14908-B016-4D5E-AEA7-D54DB9070BC6}">
   <dimension ref="A1:AC5"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="15.140625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.28515625" collapsed="true"/>
-    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
     <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="29" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3165,7 +3793,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -3201,7 +3829,7 @@
       </c>
       <c r="AB2" s="2"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>136</v>
       </c>
@@ -3236,7 +3864,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>136</v>
       </c>
@@ -3271,7 +3899,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>136</v>
       </c>
@@ -3312,37 +3940,37 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822FCC47-1993-44A8-9BE0-581A41644C90}">
   <dimension ref="A1:AC5"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="15.140625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.28515625" collapsed="true"/>
-    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
     <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="29" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3428,7 +4056,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -3464,7 +4092,7 @@
       </c>
       <c r="AB2" s="2"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>136</v>
       </c>
@@ -3499,7 +4127,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>136</v>
       </c>
@@ -3534,7 +4162,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>136</v>
       </c>
@@ -3568,171 +4196,6 @@
       <c r="W5" s="1" t="s">
         <v>125</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0550F98D-701F-463B-8524-B8E5F73F2D8E}">
-  <dimension ref="A1:AC5"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.28515625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="15.140625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.28515625" collapsed="true"/>
-    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
-    <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="29" max="16384" style="1" width="15.7109375" collapsed="true"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2"/>
-      <c r="B2"/>
-      <c r="C2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AB2" s="2"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3"/>
-      <c r="B3"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4"/>
-      <c r="B4"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5"/>
-      <c r="B5"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -3740,37 +4203,36 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30327A80-5D3D-4DEF-87CB-A4BDC28D6002}">
-  <dimension ref="A1:AD5"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0550F98D-701F-463B-8524-B8E5F73F2D8E}">
+  <dimension ref="A1:AC5"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="15.140625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.28515625" collapsed="true"/>
-    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
     <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="29" max="29" customWidth="true" style="1" width="28.140625" collapsed="true"/>
-    <col min="30" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3855,19 +4317,12 @@
       <c r="AB1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row ht="30" r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" t="s">
-        <v>161</v>
-      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2"/>
+      <c r="B2"/>
       <c r="C2" s="1" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>130</v>
@@ -3876,14 +4331,11 @@
         <v>123</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="T2" s="1" t="s">
         <v>127</v>
       </c>
@@ -3897,56 +4349,16 @@
         <v>125</v>
       </c>
       <c r="AB2" s="2"/>
-      <c r="AC2" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3"/>
+      <c r="B3"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4"/>
       <c r="B4"/>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5"/>
       <c r="B5"/>
     </row>
@@ -3956,393 +4368,448 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FB57A2-D7E3-4332-BF3A-D9FD91EC8308}">
-  <dimension ref="A1:AY2"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30327A80-5D3D-4DEF-87CB-A4BDC28D6002}">
+  <dimension ref="A1:AD5"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="49.42578125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="4.0" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="8.28515625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="6.85546875" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="13.85546875" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.42578125" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="5.5703125" collapsed="true"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="6.140625" collapsed="true"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="14.7109375" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="23.85546875" collapsed="true"/>
-    <col min="18" max="23" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="24" max="24" customWidth="true" style="1" width="9.85546875" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="6.85546875" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="29" max="29" style="1" width="15.7109375" collapsed="true"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="32" max="33" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="34" max="39" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="41" max="41" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="17.28515625" collapsed="true"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="45" max="46" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="51" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="29" max="29" customWidth="true" style="1" width="28.109375" collapsed="true"/>
+    <col min="30" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>129</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>122</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row ht="28.8" r="2" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="2"/>
+      <c r="H2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="U2" s="1" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AX2" s="2"/>
+      <c r="H3" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A4"/>
+      <c r="B4"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A5"/>
+      <c r="B5"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <headerFooter>
-    <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6029C9A2-9E58-4FB9-972D-7B9E934718A7}">
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FB57A2-D7E3-4332-BF3A-D9FD91EC8308}">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="56.42578125" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="1" width="49.44140625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="4.0" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="8.33203125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="13.88671875" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.44140625" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="5.5546875" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="6.109375" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="14.6640625" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="23.88671875" collapsed="true"/>
+    <col min="18" max="23" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="1" width="9.88671875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.6640625" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="29" max="29" style="1" width="15.6640625" collapsed="true"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="34" max="39" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="41" max="41" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="17.33203125" collapsed="true"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="45" max="46" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="51" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="3"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="3"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" s="3"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="3"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B15" s="3"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B16" s="3"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B17" s="3"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="3"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>158</v>
-      </c>
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="2"/>
+      <c r="U2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX2" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -4353,183 +4820,192 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F5F0A8-DFAA-493B-B07B-97C59CBB0D66}">
-  <dimension ref="A1:AC2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6029C9A2-9E58-4FB9-972D-7B9E934718A7}">
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="6.5703125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.85546875" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="19.28515625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="10.42578125" collapsed="true"/>
-    <col min="9" max="17" bestFit="true" customWidth="true" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="8.5703125" collapsed="true"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.28515625" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" width="6.42578125" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="6.0" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="8.140625" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="56.44140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row customFormat="1" ht="45" r="2" s="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AB2" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="3"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="3"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="3"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="3"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>158</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <headerFooter>
+    <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{133992E5-F2D4-42EB-B2FB-D66167060930}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F5F0A8-DFAA-493B-B07B-97C59CBB0D66}">
   <dimension ref="A1:AC2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="6.5703125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.85546875" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.88671875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="10.42578125" collapsed="true"/>
-    <col min="9" max="17" bestFit="true" customWidth="true" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="8.5703125" collapsed="true"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.28515625" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" width="6.42578125" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="10.44140625" collapsed="true"/>
+    <col min="9" max="17" bestFit="true" customWidth="true" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.5546875" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.33203125" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" width="6.0" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="8.140625" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row customFormat="1" r="1" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -4615,15 +5091,15 @@
         <v>80</v>
       </c>
     </row>
-    <row customFormat="1" r="2" s="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row customFormat="1" ht="28.8" r="2" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>130</v>
@@ -4632,13 +5108,10 @@
         <v>152</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>127</v>

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
@@ -1,54 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E5A5C9-77A2-445C-9695-5115776EE781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{B4E5A5C9-77A2-445C-9695-5115776EE781}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{19E085DA-5ADF-4B16-9D78-B410FD3FCE3D}"/>
+    <workbookView activeTab="2" windowHeight="12456" windowWidth="23256" xWindow="-108" xr2:uid="{19E085DA-5ADF-4B16-9D78-B410FD3FCE3D}" yWindow="-108"/>
   </bookViews>
   <sheets>
-    <sheet name="PayNowCC" sheetId="1" r:id="rId1"/>
-    <sheet name="PayNowCCNoCF" sheetId="22" r:id="rId2"/>
-    <sheet name="VerifyPaymentConfPayNowCC" sheetId="31" r:id="rId3"/>
-    <sheet name="VerifyReceiptCC" sheetId="32" r:id="rId4"/>
-    <sheet name="PayNowCCSCF" sheetId="5" r:id="rId5"/>
-    <sheet name="PayNowCCDCF" sheetId="6" r:id="rId6"/>
-    <sheet name="DCFVerbiage" sheetId="8" r:id="rId7"/>
-    <sheet name="OverUnderPay" sheetId="9" r:id="rId8"/>
-    <sheet name="MissingCC" sheetId="4" r:id="rId9"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId10"/>
-    <sheet name="NoModifyAmount" sheetId="10" r:id="rId11"/>
-    <sheet name="NoOverPay" sheetId="11" r:id="rId12"/>
-    <sheet name="SCFVerbiage" sheetId="7" r:id="rId13"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId14"/>
-    <sheet name="NoModifyAmountCC" sheetId="12" r:id="rId15"/>
-    <sheet name="NoModifyBillingAddressCC" sheetId="13" r:id="rId16"/>
-    <sheet name="CCDeferredCC" sheetId="14" r:id="rId17"/>
-    <sheet name="CancelStaticTextDeferredCC" sheetId="27" r:id="rId18"/>
-    <sheet name="CancelSuccessDeferredCC" sheetId="28" r:id="rId19"/>
-    <sheet name="ModifyStaticTextDeferredCC" sheetId="29" r:id="rId20"/>
-    <sheet name="ModifySuccessDeferredCC" sheetId="30" r:id="rId21"/>
-    <sheet name="CMCAutopayCC" sheetId="15" r:id="rId22"/>
-    <sheet name="CancelStaticTextAutopayCC" sheetId="23" r:id="rId23"/>
-    <sheet name="CancelSuccessAutopayCC" sheetId="24" r:id="rId24"/>
-    <sheet name="ModifyStaticTextAutopayCC" sheetId="25" r:id="rId25"/>
-    <sheet name="ModifySuccessAutopayCC" sheetId="26" r:id="rId26"/>
-    <sheet name="PayNowCreditCardDCF" sheetId="16" r:id="rId27"/>
-    <sheet name="ModifyPaymentsCC1" sheetId="20" r:id="rId28"/>
-    <sheet name="ModifyPaymentsCC2" sheetId="21" r:id="rId29"/>
-    <sheet name="PayNowCreditCardSCF" sheetId="17" r:id="rId30"/>
-    <sheet name="DCFCCVerbiage" sheetId="18" r:id="rId31"/>
-    <sheet name="SCFCCVerbiage" sheetId="19" r:id="rId32"/>
+    <sheet name="PayNowCC" r:id="rId1" sheetId="1"/>
+    <sheet name="PayNowCCNoCF" r:id="rId2" sheetId="22"/>
+    <sheet name="VerifyPaymentConfPayNowCC" r:id="rId3" sheetId="31"/>
+    <sheet name="VerifyReceiptCC" r:id="rId4" sheetId="32"/>
+    <sheet name="PayNowCCSCF" r:id="rId5" sheetId="5"/>
+    <sheet name="PayNowCCDCF" r:id="rId6" sheetId="6"/>
+    <sheet name="DCFVerbiage" r:id="rId7" sheetId="8"/>
+    <sheet name="OverUnderPay" r:id="rId8" sheetId="9"/>
+    <sheet name="MissingCC" r:id="rId9" sheetId="4"/>
+    <sheet name="Sheet2" r:id="rId10" sheetId="3"/>
+    <sheet name="NoModifyAmount" r:id="rId11" sheetId="10"/>
+    <sheet name="NoOverPay" r:id="rId12" sheetId="11"/>
+    <sheet name="SCFVerbiage" r:id="rId13" sheetId="7"/>
+    <sheet name="Sheet1" r:id="rId14" sheetId="2"/>
+    <sheet name="NoModifyAmountCC" r:id="rId15" sheetId="12"/>
+    <sheet name="NoModifyBillingAddressCC" r:id="rId16" sheetId="13"/>
+    <sheet name="CCDeferredCC" r:id="rId17" sheetId="14"/>
+    <sheet name="CancelStaticTextDeferredCC" r:id="rId18" sheetId="27"/>
+    <sheet name="CancelSuccessDeferredCC" r:id="rId19" sheetId="28"/>
+    <sheet name="ModifyStaticTextDeferredCC" r:id="rId20" sheetId="29"/>
+    <sheet name="ModifySuccessDeferredCC" r:id="rId21" sheetId="30"/>
+    <sheet name="CMCAutopayCC" r:id="rId22" sheetId="15"/>
+    <sheet name="CancelStaticTextAutopayCC" r:id="rId23" sheetId="23"/>
+    <sheet name="CancelSuccessAutopayCC" r:id="rId24" sheetId="24"/>
+    <sheet name="ModifyStaticTextAutopayCC" r:id="rId25" sheetId="25"/>
+    <sheet name="ModifySuccessAutopayCC" r:id="rId26" sheetId="26"/>
+    <sheet name="PayNowCreditCardDCF" r:id="rId27" sheetId="16"/>
+    <sheet name="ModifyPaymentsCC1" r:id="rId28" sheetId="20"/>
+    <sheet name="ModifyPaymentsCC2" r:id="rId29" sheetId="21"/>
+    <sheet name="PayNowCreditCardSCF" r:id="rId30" sheetId="17"/>
+    <sheet name="DCFCCVerbiage" r:id="rId31" sheetId="18"/>
+    <sheet name="SCFCCVerbiage" r:id="rId32" sheetId="19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="276">
   <si>
     <t>Notes</t>
   </si>
@@ -694,12 +694,211 @@
   </si>
   <si>
     <t>Wed Apr 01 21:49:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Mon Apr 13 20:58:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 14 22:12:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:20:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:36:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:42:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:43:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:47:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:51:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:55:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:56:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:57:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:58:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:59:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:00:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:04:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:08:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:09:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:10:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:20:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:23:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:24:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:34:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:38:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:41:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:42:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 21:45:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 21:52:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 21:59:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:03:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:07:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:12:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:13:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:14:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:15:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:16:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:17:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:21:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:25:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:37:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:38:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:40:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:41:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:57:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:01:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:02:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:04:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:05:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:07:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:10:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:12:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:13:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:15:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:20:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:22:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:23:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:24:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:30:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:33:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:37:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:41:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:49:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:54:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 20:35:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 20:48:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 20:57:23 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -754,25 +953,25 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" borderId="0" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" quotePrefix="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -789,10 +988,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -827,7 +1026,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -879,7 +1078,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -990,21 +1189,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1021,7 +1220,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1073,32 +1272,32 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4684B99E-74C7-4C50-809D-02154653C064}">
-  <dimension ref="A1:N7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4684B99E-74C7-4C50-809D-02154653C064}">
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="43.88671875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="12.44140625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="15.6640625" style="1" collapsed="1"/>
-    <col min="8" max="8" width="10.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="17.6640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="23" style="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="14.44140625" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="15.88671875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="15" max="16384" width="15.6640625" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="43.88671875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="12.44140625" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="23.0" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="14.44140625" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="15.88671875" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="15" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1145,12 +1344,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>241</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>181</v>
@@ -1183,12 +1382,12 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>242</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>181</v>
@@ -1221,12 +1420,12 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>243</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>181</v>
@@ -1264,7 +1463,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>184</v>
@@ -1305,7 +1504,7 @@
         <v>136</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>184</v>
@@ -1346,7 +1545,7 @@
         <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>184</v>
@@ -1384,8 +1583,8 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1393,11 +1592,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6029C9A2-9E58-4FB9-972D-7B9E934718A7}">
-  <dimension ref="A1:B26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6029C9A2-9E58-4FB9-972D-7B9E934718A7}">
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="56.44140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="56.44140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -1546,7 +1745,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1554,31 +1753,31 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F5F0A8-DFAA-493B-B07B-97C59CBB0D66}">
-  <dimension ref="A1:AB2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F5F0A8-DFAA-493B-B07B-97C59CBB0D66}">
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.44140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="17" width="7.88671875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="8.88671875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="8.5546875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="17.33203125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="6.5546875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="8.109375" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="24" width="7.44140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="25" max="26" width="6.44140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="8.109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.88671875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="19.33203125" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="10.44140625" collapsed="true"/>
+    <col min="9" max="17" bestFit="true" customWidth="true" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.5546875" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.33203125" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="6.0" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row customFormat="1" r="1" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -1664,7 +1863,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row customFormat="1" ht="28.8" r="2" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -1701,36 +1900,36 @@
       <c r="AB2" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{133992E5-F2D4-42EB-B2FB-D66167060930}">
-  <dimension ref="A1:AB2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{133992E5-F2D4-42EB-B2FB-D66167060930}">
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.44140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="17" width="7.88671875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="8.88671875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="8.5546875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="17.33203125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="6.5546875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="8.109375" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="24" width="7.44140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="25" max="26" width="6.44140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="8.109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.88671875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="19.33203125" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="10.44140625" collapsed="true"/>
+    <col min="9" max="17" bestFit="true" customWidth="true" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.5546875" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.33203125" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="6.0" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row customFormat="1" r="1" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -1816,7 +2015,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row customFormat="1" r="2" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -1856,38 +2055,38 @@
       <c r="AB2" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0998B4B-1379-4C62-AAAC-69FB8C23F4B6}">
-  <dimension ref="A1:AB5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0998B4B-1379-4C62-AAAC-69FB8C23F4B6}">
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="15.6640625" style="1" collapsed="1"/>
-    <col min="8" max="8" width="10.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="13.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="17" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="8.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="17.6640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="23" style="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="6.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="8.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="24" width="7.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="25" max="26" width="9.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="16384" width="15.6640625" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -2023,53 +2222,53 @@
       <c r="B5"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CECF72-ED76-4A08-B368-44E780FE04C9}">
-  <dimension ref="A1:AX4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CECF72-ED76-4A08-B368-44E780FE04C9}">
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="4" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="8.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="8.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="7" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="6.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="13.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="9" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="9.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="5.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="6.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="14.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="23.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="23" width="9.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="9.88671875" style="1" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="6.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="9.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="10.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="6.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="15.6640625" style="1" collapsed="1"/>
-    <col min="30" max="30" width="10.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="31" max="31" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="32" max="33" width="9.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="34" max="39" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="40" max="40" width="8.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="41" max="41" width="17.6640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="42" max="42" width="17.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="43" max="43" width="6.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="44" max="44" width="8.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="45" max="46" width="7.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="47" max="48" width="9.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="49" max="49" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="50" max="50" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="51" max="16384" width="15.6640625" style="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="38.5546875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="4.0" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="8.33203125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="13.88671875" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.44140625" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="5.5546875" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="6.109375" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="14.6640625" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="23.88671875" collapsed="true"/>
+    <col min="18" max="23" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="1" width="9.88671875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.6640625" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="29" max="29" style="1" width="15.6640625" collapsed="true"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="34" max="39" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="41" max="41" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="17.33203125" collapsed="true"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="45" max="46" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="51" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.3">
@@ -2529,7 +2728,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -2537,11 +2736,11 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E9DE92-B397-44B0-AEC9-F8D25811CB54}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E9DE92-B397-44B0-AEC9-F8D25811CB54}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2585,12 +2784,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+    <row ht="100.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
@@ -2630,16 +2829,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5A0641-6BD7-468B-84F0-EE792C70A080}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5A0641-6BD7-468B-84F0-EE792C70A080}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2683,12 +2882,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+    <row ht="100.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
@@ -2728,19 +2927,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D73A527-72BD-4591-A2D4-2CEF61283D2F}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D73A527-72BD-4591-A2D4-2CEF61283D2F}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2784,12 +2983,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2827,19 +3026,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6E154C7-CD3E-4C9D-88A3-7DE63AC4DF57}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6E154C7-CD3E-4C9D-88A3-7DE63AC4DF57}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2883,12 +3082,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2926,19 +3125,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEEAEF2C-8842-4627-86DE-B47E4843BEBC}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEEAEF2C-8842-4627-86DE-B47E4843BEBC}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2982,12 +3181,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3025,16 +3224,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8552FB6B-D1DF-4DF4-9CDC-DC482F51F66E}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8552FB6B-D1DF-4DF4-9CDC-DC482F51F66E}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3078,7 +3277,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+    <row ht="115.2" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -3119,19 +3318,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F006E898-806E-40BD-844F-24C691CDEE15}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F006E898-806E-40BD-844F-24C691CDEE15}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3175,12 +3374,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>269</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3218,19 +3417,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA3C1A8-9598-4860-B2FD-3F2531B8283E}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA3C1A8-9598-4860-B2FD-3F2531B8283E}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3274,12 +3473,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>270</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3317,16 +3516,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF51F7AD-B3C1-42AF-94A4-9027DD404D74}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF51F7AD-B3C1-42AF-94A4-9027DD404D74}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3375,7 +3574,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>257</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3411,16 +3610,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30FA598-5BA2-4C47-B402-30C5508F2C97}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30FA598-5BA2-4C47-B402-30C5508F2C97}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3469,7 +3668,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3505,16 +3704,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41DCD81-93AB-468D-BB89-6D7AEFF24AFE}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41DCD81-93AB-468D-BB89-6D7AEFF24AFE}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3563,7 +3762,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3599,16 +3798,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7212A3A6-193F-447F-ADA2-6AEA83AE9AE7}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7212A3A6-193F-447F-ADA2-6AEA83AE9AE7}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3657,7 +3856,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>273</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3693,16 +3892,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0E9863-D4FC-4D93-85C1-403C55CF2F69}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0E9863-D4FC-4D93-85C1-403C55CF2F69}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3751,7 +3950,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3787,19 +3986,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAE4061-05C7-45C5-8300-61EB089304F4}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAE4061-05C7-45C5-8300-61EB089304F4}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.88671875" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" customWidth="true" width="19.88671875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3848,7 +4047,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3884,16 +4083,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53E0D33-A959-464C-9A30-B01B5F6EAEC6}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53E0D33-A959-464C-9A30-B01B5F6EAEC6}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3970,16 +4169,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2B6DA3-9B51-4304-9318-F6DFDE44D446}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2B6DA3-9B51-4304-9318-F6DFDE44D446}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -4056,16 +4255,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC03E43-4358-4D9D-8234-CC138C0C879E}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC03E43-4358-4D9D-8234-CC138C0C879E}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -4109,12 +4308,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+    <row ht="115.2" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>272</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>181</v>
@@ -4150,16 +4349,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CCF0244-D738-49E7-A19C-75065FE186E2}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CCF0244-D738-49E7-A19C-75065FE186E2}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -4208,7 +4407,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4244,16 +4443,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24FF721F-C1CF-4DC8-8195-832F8368F224}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24FF721F-C1CF-4DC8-8195-832F8368F224}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -4302,7 +4501,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4338,16 +4537,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4992758E-A1F9-4281-AE93-21063312FF32}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4992758E-A1F9-4281-AE93-21063312FF32}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -4396,7 +4595,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4432,47 +4631,47 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B94414-48CE-410C-8F8E-F2296E62DA0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B94414-48CE-410C-8F8E-F2296E62DA0D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCE14908-B016-4D5E-AEA7-D54DB9070BC6}">
-  <dimension ref="A1:AB5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCE14908-B016-4D5E-AEA7-D54DB9070BC6}">
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="15.6640625" style="1" collapsed="1"/>
-    <col min="8" max="8" width="10.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="13.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="17" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="8.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="17.6640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="23" style="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="6.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="8.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="24" width="7.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="25" max="26" width="9.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="16384" width="15.6640625" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -4704,38 +4903,38 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822FCC47-1993-44A8-9BE0-581A41644C90}">
-  <dimension ref="A1:AB5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822FCC47-1993-44A8-9BE0-581A41644C90}">
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="15.6640625" style="1" collapsed="1"/>
-    <col min="8" max="8" width="10.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="13.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="17" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="8.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="17.6640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="23" style="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="6.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="8.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="24" width="7.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="25" max="26" width="9.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="16384" width="15.6640625" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -4966,38 +5165,38 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0550F98D-701F-463B-8524-B8E5F73F2D8E}">
-  <dimension ref="A1:AB5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0550F98D-701F-463B-8524-B8E5F73F2D8E}">
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="15.6640625" style="1" collapsed="1"/>
-    <col min="8" max="8" width="10.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="13.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="17" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="8.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="17.6640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="23" style="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="6.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="8.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="24" width="7.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="25" max="26" width="9.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="16384" width="15.6640625" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -5131,39 +5330,39 @@
       <c r="B5"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30327A80-5D3D-4DEF-87CB-A4BDC28D6002}">
-  <dimension ref="A1:AC5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30327A80-5D3D-4DEF-87CB-A4BDC28D6002}">
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="15.6640625" style="1" collapsed="1"/>
-    <col min="8" max="8" width="10.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="13.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="17" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="8.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="17.6640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="23" style="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="6.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="8.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="24" width="7.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="25" max="26" width="9.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="28.109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="30" max="16384" width="15.6640625" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="29" max="29" customWidth="true" style="1" width="28.109375" collapsed="true"/>
+    <col min="30" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -5255,7 +5454,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -5347,53 +5546,53 @@
       <c r="B5"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FB57A2-D7E3-4332-BF3A-D9FD91EC8308}">
-  <dimension ref="A1:AX2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FB57A2-D7E3-4332-BF3A-D9FD91EC8308}">
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="49.44140625" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="4" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="8.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="8.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="7" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="6.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="13.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="9" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="9.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="5.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="6.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="14.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="23.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="23" width="9.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="9.88671875" style="1" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="6.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="9.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="10.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="6.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="15.6640625" style="1" collapsed="1"/>
-    <col min="30" max="30" width="10.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="31" max="31" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="32" max="33" width="9.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="34" max="39" width="7.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="40" max="40" width="8.88671875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="41" max="41" width="17.6640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="42" max="42" width="17.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="43" max="43" width="6.5546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="44" max="44" width="8.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="45" max="46" width="7.44140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="47" max="48" width="9.109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="49" max="49" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="50" max="50" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="51" max="16384" width="15.6640625" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="49.44140625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="4.0" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="8.33203125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="13.88671875" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.44140625" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="5.5546875" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="6.109375" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="14.6640625" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="23.88671875" collapsed="true"/>
+    <col min="18" max="23" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="1" width="9.88671875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.6640625" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="29" max="29" style="1" width="15.6640625" collapsed="true"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="34" max="39" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="41" max="41" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="17.33203125" collapsed="true"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="45" max="46" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="51" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.3">
@@ -5580,7 +5779,7 @@
       <c r="AX2" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="328">
   <si>
     <t>Notes</t>
   </si>
@@ -892,6 +892,162 @@
   </si>
   <si>
     <t>Mon May 04 20:57:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:02:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:09:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:10:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:11:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:12:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:30:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:31:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:31:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:32:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:36:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:40:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:44:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:45:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:46:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:47:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:48:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:49:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:53:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:57:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:03:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:05:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:06:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:22:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:29:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:31:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:33:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:34:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:35:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:48:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:50:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:51:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:52:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:59:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:02:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:05:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:06:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:08:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:09:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:21:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:22:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:23:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:24:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:47:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:52:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:40:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:52:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 20:01:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 20:03:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 20:07:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 16 19:46:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 16 19:48:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 16 19:52:40 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1349,7 +1505,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>287</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>181</v>
@@ -1387,7 +1543,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>288</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>181</v>
@@ -1425,7 +1581,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>181</v>
@@ -1463,7 +1619,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>184</v>
@@ -1504,7 +1660,7 @@
         <v>136</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>291</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>184</v>
@@ -1545,7 +1701,7 @@
         <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>184</v>
@@ -2789,7 +2945,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
@@ -2887,7 +3043,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
@@ -2988,7 +3144,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>237</v>
+        <v>327</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3087,7 +3243,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3186,7 +3342,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3379,7 +3535,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3478,7 +3634,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>317</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3574,7 +3730,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3668,7 +3824,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>294</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3762,7 +3918,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>274</v>
+        <v>324</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3853,10 +4009,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="B2" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3950,7 +4106,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4047,7 +4203,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4313,7 +4469,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>181</v>
@@ -4407,7 +4563,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4501,7 +4657,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4595,7 +4751,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="330">
   <si>
     <t>Notes</t>
   </si>
@@ -1048,6 +1048,12 @@
   </si>
   <si>
     <t>Tue Jun 16 19:52:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 21:01:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 21:04:47 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1436,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4684B99E-74C7-4C50-809D-02154653C064}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
@@ -1501,10 +1507,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="1">
         <v>287</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1539,10 +1545,10 @@
       </c>
     </row>
     <row ht="28.8" r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="1">
         <v>288</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1577,10 +1583,10 @@
       </c>
     </row>
     <row ht="28.8" r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="1">
         <v>289</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1615,10 +1621,10 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="1">
         <v>290</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1656,10 +1662,10 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="1">
         <v>291</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1697,10 +1703,10 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="1">
         <v>292</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1749,154 +1755,154 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6029C9A2-9E58-4FB9-972D-7B9E934718A7}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="56.44140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>100</v>
       </c>
       <c r="B1" s="3"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>101</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>102</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>103</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>104</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>111</v>
       </c>
       <c r="B6" s="3"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>112</v>
       </c>
       <c r="B7" s="3"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>113</v>
       </c>
       <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>114</v>
       </c>
       <c r="B9" s="3"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>115</v>
       </c>
       <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>120</v>
       </c>
       <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>121</v>
       </c>
       <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>139</v>
       </c>
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>140</v>
       </c>
       <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>155</v>
       </c>
       <c r="B23" s="3"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>158</v>
       </c>
     </row>
@@ -1910,7 +1916,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F5F0A8-DFAA-493B-B07B-97C59CBB0D66}">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
@@ -2020,10 +2026,10 @@
       </c>
     </row>
     <row customFormat="1" ht="28.8" r="2" s="1" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>172</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2062,7 +2068,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{133992E5-F2D4-42EB-B2FB-D66167060930}">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
@@ -2172,10 +2178,10 @@
       </c>
     </row>
     <row customFormat="1" r="2" s="1" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>163</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2217,7 +2223,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0998B4B-1379-4C62-AAAC-69FB8C23F4B6}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
@@ -2332,10 +2338,10 @@
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B2"/>
+      <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
         <v>124</v>
       </c>
@@ -2366,16 +2372,16 @@
       <c r="AB2" s="2"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3"/>
-      <c r="B3"/>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4"/>
-      <c r="B4"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5"/>
-      <c r="B5"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2384,7 +2390,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CECF72-ED76-4A08-B368-44E780FE04C9}">
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="38.5546875" collapsed="true"/>
@@ -2893,7 +2899,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E9DE92-B397-44B0-AEC9-F8D25811CB54}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2941,10 +2947,10 @@
       </c>
     </row>
     <row ht="100.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>284</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2991,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5A0641-6BD7-468B-84F0-EE792C70A080}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3039,10 +3045,10 @@
       </c>
     </row>
     <row ht="100.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -3089,7 +3095,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D73A527-72BD-4591-A2D4-2CEF61283D2F}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
@@ -3140,11 +3146,11 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
-        <v>327</v>
+      <c r="B2" t="s" s="0">
+        <v>329</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3188,7 +3194,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6E154C7-CD3E-4C9D-88A3-7DE63AC4DF57}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
@@ -3239,10 +3245,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>308</v>
       </c>
       <c r="C2" s="2"/>
@@ -3287,7 +3293,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEEAEF2C-8842-4627-86DE-B47E4843BEBC}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
@@ -3338,10 +3344,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>309</v>
       </c>
       <c r="C2" s="2"/>
@@ -3386,7 +3392,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8552FB6B-D1DF-4DF4-9CDC-DC482F51F66E}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3434,10 +3440,10 @@
       </c>
     </row>
     <row ht="115.2" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>207</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -3480,7 +3486,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F006E898-806E-40BD-844F-24C691CDEE15}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
@@ -3531,10 +3537,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>313</v>
       </c>
       <c r="C2" s="2"/>
@@ -3579,7 +3585,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA3C1A8-9598-4860-B2FD-3F2531B8283E}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
@@ -3630,10 +3636,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>317</v>
       </c>
       <c r="C2" s="2"/>
@@ -3678,7 +3684,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF51F7AD-B3C1-42AF-94A4-9027DD404D74}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3726,10 +3732,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>276</v>
       </c>
       <c r="C2" s="2"/>
@@ -3772,7 +3778,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30FA598-5BA2-4C47-B402-30C5508F2C97}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3820,10 +3826,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>294</v>
       </c>
       <c r="C2" s="2"/>
@@ -3866,7 +3872,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41DCD81-93AB-468D-BB89-6D7AEFF24AFE}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3914,10 +3920,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>324</v>
       </c>
       <c r="C2" s="2"/>
@@ -3960,7 +3966,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7212A3A6-193F-447F-ADA2-6AEA83AE9AE7}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4008,10 +4014,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>210</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>297</v>
       </c>
       <c r="C2" s="2"/>
@@ -4054,7 +4060,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0E9863-D4FC-4D93-85C1-403C55CF2F69}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4102,10 +4108,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>323</v>
       </c>
       <c r="C2" s="2"/>
@@ -4148,7 +4154,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAE4061-05C7-45C5-8300-61EB089304F4}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="19.88671875" collapsed="true"/>
@@ -4199,10 +4205,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>286</v>
       </c>
       <c r="C2" s="2"/>
@@ -4245,7 +4251,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53E0D33-A959-464C-9A30-B01B5F6EAEC6}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4331,7 +4337,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2B6DA3-9B51-4304-9318-F6DFDE44D446}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4417,7 +4423,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC03E43-4358-4D9D-8234-CC138C0C879E}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4465,10 +4471,10 @@
       </c>
     </row>
     <row ht="115.2" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>319</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -4511,7 +4517,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CCF0244-D738-49E7-A19C-75065FE186E2}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4559,10 +4565,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>293</v>
       </c>
       <c r="C2" s="2"/>
@@ -4605,7 +4611,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24FF721F-C1CF-4DC8-8195-832F8368F224}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4653,10 +4659,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>298</v>
       </c>
       <c r="C2" s="2"/>
@@ -4699,7 +4705,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4992758E-A1F9-4281-AE93-21063312FF32}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4747,10 +4753,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>299</v>
       </c>
       <c r="C2" s="2"/>
@@ -4802,7 +4808,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCE14908-B016-4D5E-AEA7-D54DB9070BC6}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
@@ -4917,10 +4923,10 @@
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="1">
         <v>164</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -4953,10 +4959,10 @@
       <c r="AB2" s="2"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="1">
         <v>165</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -4988,10 +4994,10 @@
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="1">
         <v>166</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -5023,10 +5029,10 @@
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="1">
         <v>167</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -5065,7 +5071,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822FCC47-1993-44A8-9BE0-581A41644C90}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
@@ -5180,10 +5186,10 @@
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="1">
         <v>168</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5216,10 +5222,10 @@
       <c r="AB2" s="2"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="1">
         <v>169</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -5251,10 +5257,10 @@
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="1">
         <v>170</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -5286,10 +5292,10 @@
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="1">
         <v>171</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -5327,7 +5333,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0550F98D-701F-463B-8524-B8E5F73F2D8E}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
@@ -5442,8 +5448,8 @@
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2"/>
-      <c r="B2"/>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
         <v>124</v>
       </c>
@@ -5474,16 +5480,16 @@
       <c r="AB2" s="2"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3"/>
-      <c r="B3"/>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4"/>
-      <c r="B4"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5"/>
-      <c r="B5"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -5492,7 +5498,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30327A80-5D3D-4DEF-87CB-A4BDC28D6002}">
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
@@ -5611,10 +5617,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="1">
         <v>161</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5653,10 +5659,10 @@
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>136</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="1">
         <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -5694,12 +5700,12 @@
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4"/>
-      <c r="B4"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5"/>
-      <c r="B5"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -5708,7 +5714,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FB57A2-D7E3-4332-BF3A-D9FD91EC8308}">
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AX2"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="49.44140625" collapsed="true"/>
